--- a/docs/custos/databricks_cost_calculator_simulacao.xlsx
+++ b/docs/custos/databricks_cost_calculator_simulacao.xlsx
@@ -63,6 +63,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="D6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Premissa técnica: DBU/hora varia pelo tipo e tamanho exato da instância. Confirmar na calculadora oficial da Databricks.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Premissa técnica: DBU/hora varia pelo tipo e tamanho exato da instância. Confirmar na calculadora oficial da Databricks.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E3" authorId="0">
       <text>
         <r>
@@ -99,12 +123,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="E6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fonte: Databricks Pricing Calculator (Azure, Premium), consultado em 30/07/2026.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fonte: Databricks Pricing Calculator (Azure, Premium), consultado em 30/07/2026.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t xml:space="preserve">Simulação — Databricks Pricing Calculator</t>
   </si>
@@ -211,6 +259,12 @@
     <t xml:space="preserve">SQL Compute</t>
   </si>
   <si>
+    <t xml:space="preserve">Job mensal — fechamento (ADR-006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job de limpeza — retenção Landing Zone (ADR-009)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total mensal (USD)</t>
   </si>
   <si>
@@ -257,6 +311,12 @@
   </si>
   <si>
     <t xml:space="preserve">Photon + warehouse maior reduz latência de dashboards/Genie, mas dobra o consumo de DBU por hora.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job mensal (ADR-006) e Job de limpeza da Landing Zone (ADR-009) têm custo residual e não variam por cenário de compute — são tratados uma única vez na aba Simulacao_Calculadora, não duplicados aqui para não inflar a comparação.</t>
   </si>
 </sst>
 </file>
@@ -916,7 +976,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:H8"/>
+  <dimension ref="A2:H10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1038,22 +1098,78 @@
         <v>52.8</v>
       </c>
     </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <f aca="false">D6*F6</f>
+        <v>0.05</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <f aca="false">G6*E6</f>
+        <v>0.0075</v>
+      </c>
+    </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <f aca="false">SUM(H3:H5)</f>
-        <v>59.1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="15" t="n">
-        <f aca="false">H7*12</f>
-        <v>709.2</v>
+      <c r="B7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <f aca="false">D7*F7</f>
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <f aca="false">G7*E7</f>
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <f aca="false">SUM(H3:H7)</f>
+        <v>59.3325</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <f aca="false">H9*12</f>
+        <v>711.99</v>
       </c>
     </row>
   </sheetData>
@@ -1073,7 +1189,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:D10"/>
+  <dimension ref="A2:D14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1082,35 +1198,35 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="13" t="n">
         <f aca="false">1*12*0.15</f>
@@ -1127,7 +1243,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" s="13" t="n">
         <f aca="false">1*30*0.15</f>
@@ -1144,7 +1260,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">4*40*0.22</f>
@@ -1161,7 +1277,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">SUM(B4:B6)</f>
@@ -1178,7 +1294,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">B7*12</f>
@@ -1195,19 +1311,41 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>50</v>
-      </c>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:D14"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
